--- a/reports/셀린느/history/2026-05-07/셀린느_training_mgf_report.xlsx
+++ b/reports/셀린느/history/2026-05-07/셀린느_training_mgf_report.xlsx
@@ -84,501 +84,504 @@
     <t>Scania 2</t>
   </si>
   <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>1위</t>
+  </si>
+  <si>
+    <t>Lv.9</t>
+  </si>
+  <si>
+    <t>30명</t>
+  </si>
+  <si>
+    <t>6경 6578조 3092억 4574만</t>
+  </si>
+  <si>
+    <t>[통합2섭1위] [토벌전1위 최종뎀10%][IN50위] 문의 [혜영]</t>
+  </si>
+  <si>
+    <t>혜영</t>
+  </si>
+  <si>
+    <t>2026.05.07</t>
+  </si>
+  <si>
+    <t>이콩</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EC%9D%B4%EC%BD%A9</t>
+  </si>
+  <si>
+    <t>Scania 28</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>2위</t>
+  </si>
+  <si>
+    <t>Lv.8</t>
+  </si>
+  <si>
+    <t>12경 997조 5244억 3604만</t>
+  </si>
+  <si>
+    <t>가입문의 - 요쯔</t>
+  </si>
+  <si>
+    <t>요쯔</t>
+  </si>
+  <si>
+    <t>딸기키우기</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%94%B8%EA%B8%B0%ED%82%A4%EC%9A%B0%EA%B8%B0</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>3위</t>
+  </si>
+  <si>
+    <t>5경 9020조 1939억 6317만</t>
+  </si>
+  <si>
+    <t>길컨에 진심인 길드입니다 길컨 자신있으신 분들만 무치z 연지임당으로 문의주세요 50조이상</t>
+  </si>
+  <si>
+    <t>무치z</t>
+  </si>
+  <si>
+    <t>LUXURY</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=LUXURY</t>
+  </si>
+  <si>
+    <t>Scania 16</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>7경 895조 6692억 2510만</t>
+  </si>
+  <si>
+    <t>*[100LV] 이상/활동,일일 업그레이드 필수* 대기 가능 문의 귓</t>
+  </si>
+  <si>
+    <t>살뽀시</t>
+  </si>
+  <si>
+    <t>고점</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EA%B3%A0%EC%A0%90</t>
+  </si>
+  <si>
+    <t>Scania 14</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>29명</t>
+  </si>
+  <si>
+    <t>7경 5026조 3174억 3719만</t>
+  </si>
+  <si>
+    <t>안녕하세요 14서버 1위길드 고점 길드 입니다.최소 투력컷은 자어 이상이며 가입 문의는 귓말 부탁드립니다</t>
+  </si>
+  <si>
+    <t>루팡잉</t>
+  </si>
+  <si>
+    <t>싸이월드</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EC%8B%B8%EC%9D%B4%EC%9B%94%EB%93%9C</t>
+  </si>
+  <si>
+    <t>Scania 11</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>Lv.11</t>
+  </si>
+  <si>
+    <t>6경 9299조 7115억 6231만</t>
+  </si>
+  <si>
+    <t>일촌 신청 환영 / BGM : 프리스타일 - Y. 길드 가입문의는 [갯수용] 귓 주세요</t>
+  </si>
+  <si>
+    <t>갯수용</t>
+  </si>
+  <si>
+    <t>라때는말이야</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%9D%BC%EB%95%8C%EB%8A%94%EB%A7%90%EC%9D%B4%EC%95%BC</t>
+  </si>
+  <si>
+    <t>Scania 35</t>
+  </si>
+  <si>
     <t>27</t>
   </si>
   <si>
-    <t>1위</t>
-  </si>
-  <si>
-    <t>Lv.9</t>
-  </si>
-  <si>
-    <t>30명</t>
-  </si>
-  <si>
-    <t>6경 6578조 3092억 4574만</t>
-  </si>
-  <si>
-    <t>[통합2섭1위] [토벌전1위 최종뎀10%][IN50위] 문의 [혜영]</t>
-  </si>
-  <si>
-    <t>혜영</t>
-  </si>
-  <si>
-    <t>2026.05.07</t>
-  </si>
-  <si>
-    <t>이콩</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%EC%9D%B4%EC%BD%A9</t>
-  </si>
-  <si>
-    <t>Scania 28</t>
+    <t>Lv.7</t>
+  </si>
+  <si>
+    <t>6경 9232조 7667억 1784만</t>
+  </si>
+  <si>
+    <t>랭킹 in70위 가입문의 (안스제.김도움.켘켘3)</t>
+  </si>
+  <si>
+    <t>안스제</t>
+  </si>
+  <si>
+    <t>member_rank_in_guild</t>
+  </si>
+  <si>
+    <t>nickname</t>
+  </si>
+  <si>
+    <t>character_key</t>
+  </si>
+  <si>
+    <t>character_url</t>
+  </si>
+  <si>
+    <t>is_master</t>
+  </si>
+  <si>
+    <t>job_name</t>
+  </si>
+  <si>
+    <t>level</t>
+  </si>
+  <si>
+    <t>combat_power</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>스타냥이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%83%80%EB%83%A5%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>신궁</t>
+  </si>
+  <si>
+    <t>115</t>
+  </si>
+  <si>
+    <t>3경 27조 8635억 7445만</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>돈스</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8F%88%EC%8A%A4</t>
+  </si>
+  <si>
+    <t>비숍</t>
+  </si>
+  <si>
+    <t>112</t>
+  </si>
+  <si>
+    <t>1경 904조 1185억 7211만</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>진자이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A7%84%EC%9E%90%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>6493조 5045억 7772만</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>말레이히어로</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A7%90%EB%A0%88%EC%9D%B4%ED%9E%88%EC%96%B4%EB%A1%9C</t>
+  </si>
+  <si>
+    <t>다크나이트</t>
+  </si>
+  <si>
+    <t>111</t>
+  </si>
+  <si>
+    <t>5860조 1812억 2503만</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>스타캐치</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%83%80%EC%BA%90%EC%B9%98</t>
+  </si>
+  <si>
+    <t>섀도어</t>
+  </si>
+  <si>
+    <t>3106조 9258억 9914만</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>빌런투킬</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B9%8C%EB%9F%B0%ED%88%AC%ED%82%AC</t>
+  </si>
+  <si>
+    <t>히어로</t>
+  </si>
+  <si>
+    <t>2011조 4544억 3476만</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>니달리신</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%88%EB%8B%AC%EB%A6%AC%EC%8B%A0</t>
+  </si>
+  <si>
+    <t>108</t>
+  </si>
+  <si>
+    <t>1042조 3116억 6204만</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>여사</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EC%82%AC</t>
+  </si>
+  <si>
+    <t>109</t>
+  </si>
+  <si>
+    <t>1007조 3178억 5658만</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>부엉이없다</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B6%80%EC%97%89%EC%9D%B4%EC%97%86%EB%8B%A4</t>
+  </si>
+  <si>
+    <t>107</t>
+  </si>
+  <si>
+    <t>874조 5211억 9379만</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>단풍노비</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%A8%ED%92%8D%EB%85%B8%EB%B9%84</t>
+  </si>
+  <si>
+    <t>869조 5677억 141만</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>약어</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%BD%EC%96%B4</t>
+  </si>
+  <si>
+    <t>보우마스터</t>
+  </si>
+  <si>
+    <t>684조 4401억 9646만</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>소소채2</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%86%8C%EC%86%8C%EC%B1%842</t>
+  </si>
+  <si>
+    <t>481조 5847억 7403만</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>닼나짱2</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%BC%EB%82%98%EC%A7%B12</t>
+  </si>
+  <si>
+    <t>106</t>
+  </si>
+  <si>
+    <t>379조 5440억 9162만</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>프리프리</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%94%84%EB%A6%AC%ED%94%84%EB%A6%AC</t>
+  </si>
+  <si>
+    <t>366조 6787억 5438만</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>꽃을든남자</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%BD%83%EC%9D%84%EB%93%A0%EB%82%A8%EC%9E%90</t>
+  </si>
+  <si>
+    <t>334조 4614억 9803만</t>
+  </si>
+  <si>
+    <t>뽀삐스</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%BD%80%EC%82%90%EC%8A%A4</t>
+  </si>
+  <si>
+    <t>275조 8357억 446만</t>
   </si>
   <si>
     <t>17</t>
   </si>
   <si>
-    <t>2위</t>
-  </si>
-  <si>
-    <t>Lv.8</t>
-  </si>
-  <si>
-    <t>11경 9267조 3727억 8819만</t>
-  </si>
-  <si>
-    <t>가입문의 - 요쯔</t>
-  </si>
-  <si>
-    <t>요쯔</t>
-  </si>
-  <si>
-    <t>딸기키우기</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%94%B8%EA%B8%B0%ED%82%A4%EC%9A%B0%EA%B8%B0</t>
-  </si>
-  <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>3위</t>
-  </si>
-  <si>
-    <t>5경 8868조 2988억 6543만</t>
-  </si>
-  <si>
-    <t>길컨에 진심인 길드입니다 길컨 자신있으신 분들만 무치z 연지임당으로 문의주세요 50조이상</t>
-  </si>
-  <si>
-    <t>무치z</t>
-  </si>
-  <si>
-    <t>LUXURY</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=LUXURY</t>
-  </si>
-  <si>
-    <t>Scania 16</t>
-  </si>
-  <si>
-    <t>24</t>
-  </si>
-  <si>
-    <t>7경 895조 6692억 2510만</t>
-  </si>
-  <si>
-    <t>*[100LV] 이상/활동,일일 업그레이드 필수* 대기 가능 문의 귓</t>
-  </si>
-  <si>
-    <t>살뽀시</t>
-  </si>
-  <si>
-    <t>고점</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%EA%B3%A0%EC%A0%90</t>
-  </si>
-  <si>
-    <t>Scania 14</t>
+    <t>잼포즈</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9E%BC%ED%8F%AC%EC%A6%88</t>
+  </si>
+  <si>
+    <t>아크메이지(썬,콜)</t>
+  </si>
+  <si>
+    <t>273조 8981억 703만</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>하후돈</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%ED%9B%84%EB%8F%88</t>
+  </si>
+  <si>
+    <t>266조 8078억 6673만</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>쾌감</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%BE%8C%EA%B0%90</t>
+  </si>
+  <si>
+    <t>254조 2629억 9000만</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>할룽</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%A0%EB%A3%BD</t>
+  </si>
+  <si>
+    <t>239조 5598억 9073만</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>두근푸근연근</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%91%90%EA%B7%BC%ED%91%B8%EA%B7%BC%EC%97%B0%EA%B7%BC</t>
+  </si>
+  <si>
+    <t>186조 7933억 7887만</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>POSCO</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=POSCO</t>
+  </si>
+  <si>
+    <t>143조 3408억 6701만</t>
   </si>
   <si>
     <t>23</t>
   </si>
   <si>
-    <t>29명</t>
-  </si>
-  <si>
-    <t>7경 5026조 3174억 3719만</t>
-  </si>
-  <si>
-    <t>안녕하세요 14서버 1위길드 고점 길드 입니다.최소 투력컷은 자어 이상이며 가입 문의는 귓말 부탁드립니다</t>
-  </si>
-  <si>
-    <t>루팡잉</t>
-  </si>
-  <si>
-    <t>싸이월드</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%EC%8B%B8%EC%9D%B4%EC%9B%94%EB%93%9C</t>
-  </si>
-  <si>
-    <t>Scania 11</t>
-  </si>
-  <si>
-    <t>26</t>
-  </si>
-  <si>
-    <t>Lv.11</t>
-  </si>
-  <si>
-    <t>6경 9162조 9519억 932만</t>
-  </si>
-  <si>
-    <t>일촌 신청 환영 / BGM : 프리스타일 - Y. 길드 가입문의는 [갯수용] 귓 주세요</t>
-  </si>
-  <si>
-    <t>갯수용</t>
-  </si>
-  <si>
-    <t>라때는말이야</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%9D%BC%EB%95%8C%EB%8A%94%EB%A7%90%EC%9D%B4%EC%95%BC</t>
-  </si>
-  <si>
-    <t>Scania 35</t>
-  </si>
-  <si>
-    <t>25</t>
-  </si>
-  <si>
-    <t>Lv.7</t>
-  </si>
-  <si>
-    <t>6경 9232조 7667억 1784만</t>
-  </si>
-  <si>
-    <t>랭킹 in70위 가입문의 (안스제.김도움.켘켘3)</t>
-  </si>
-  <si>
-    <t>안스제</t>
-  </si>
-  <si>
-    <t>member_rank_in_guild</t>
-  </si>
-  <si>
-    <t>nickname</t>
-  </si>
-  <si>
-    <t>character_key</t>
-  </si>
-  <si>
-    <t>character_url</t>
-  </si>
-  <si>
-    <t>is_master</t>
-  </si>
-  <si>
-    <t>job_name</t>
-  </si>
-  <si>
-    <t>level</t>
-  </si>
-  <si>
-    <t>combat_power</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>스타냥이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%83%80%EB%83%A5%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>N</t>
-  </si>
-  <si>
-    <t>신궁</t>
-  </si>
-  <si>
-    <t>115</t>
-  </si>
-  <si>
-    <t>3경 27조 8635억 7445만</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>돈스</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8F%88%EC%8A%A4</t>
-  </si>
-  <si>
-    <t>비숍</t>
-  </si>
-  <si>
-    <t>112</t>
-  </si>
-  <si>
-    <t>1경 904조 1185억 7211만</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>진자이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A7%84%EC%9E%90%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>6493조 5045억 7772만</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>말레이히어로</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A7%90%EB%A0%88%EC%9D%B4%ED%9E%88%EC%96%B4%EB%A1%9C</t>
-  </si>
-  <si>
-    <t>다크나이트</t>
-  </si>
-  <si>
-    <t>111</t>
-  </si>
-  <si>
-    <t>5860조 1812억 2503만</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>스타캐치</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%83%80%EC%BA%90%EC%B9%98</t>
-  </si>
-  <si>
-    <t>섀도어</t>
-  </si>
-  <si>
-    <t>3106조 9258억 9914만</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>빌런투킬</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B9%8C%EB%9F%B0%ED%88%AC%ED%82%AC</t>
-  </si>
-  <si>
-    <t>히어로</t>
-  </si>
-  <si>
-    <t>2011조 4544억 3476만</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>니달리신</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8B%88%EB%8B%AC%EB%A6%AC%EC%8B%A0</t>
-  </si>
-  <si>
-    <t>108</t>
-  </si>
-  <si>
-    <t>1042조 3116억 6204만</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>여사</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EC%82%AC</t>
-  </si>
-  <si>
-    <t>109</t>
-  </si>
-  <si>
-    <t>1007조 3178억 5658만</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>부엉이없다</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B6%80%EC%97%89%EC%9D%B4%EC%97%86%EB%8B%A4</t>
-  </si>
-  <si>
-    <t>107</t>
-  </si>
-  <si>
-    <t>874조 5211억 9379만</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>단풍노비</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8B%A8%ED%92%8D%EB%85%B8%EB%B9%84</t>
-  </si>
-  <si>
-    <t>869조 5677억 141만</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>약어</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%BD%EC%96%B4</t>
-  </si>
-  <si>
-    <t>보우마스터</t>
-  </si>
-  <si>
-    <t>684조 4401억 9646만</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>소소채2</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%86%8C%EC%86%8C%EC%B1%842</t>
-  </si>
-  <si>
-    <t>481조 5847억 7403만</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>닼나짱2</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8B%BC%EB%82%98%EC%A7%B12</t>
-  </si>
-  <si>
-    <t>106</t>
-  </si>
-  <si>
-    <t>379조 5440억 9162만</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>프리프리</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%94%84%EB%A6%AC%ED%94%84%EB%A6%AC</t>
-  </si>
-  <si>
-    <t>366조 6787억 5438만</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>꽃을든남자</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%BD%83%EC%9D%84%EB%93%A0%EB%82%A8%EC%9E%90</t>
-  </si>
-  <si>
-    <t>334조 4614억 9803만</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>뽀삐스</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%BD%80%EC%82%90%EC%8A%A4</t>
-  </si>
-  <si>
-    <t>275조 8357억 446만</t>
-  </si>
-  <si>
-    <t>잼포즈</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9E%BC%ED%8F%AC%EC%A6%88</t>
-  </si>
-  <si>
-    <t>아크메이지(썬,콜)</t>
-  </si>
-  <si>
-    <t>273조 8981억 703만</t>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>하후돈</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%ED%9B%84%EB%8F%88</t>
-  </si>
-  <si>
-    <t>266조 8078억 6673만</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>쾌감</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%BE%8C%EA%B0%90</t>
-  </si>
-  <si>
-    <t>254조 2629억 9000만</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>할룽</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%A0%EB%A3%BD</t>
-  </si>
-  <si>
-    <t>239조 5598억 9073만</t>
-  </si>
-  <si>
-    <t>21</t>
-  </si>
-  <si>
-    <t>두근푸근연근</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%91%90%EA%B7%BC%ED%91%B8%EA%B7%BC%EC%97%B0%EA%B7%BC</t>
-  </si>
-  <si>
-    <t>186조 7933억 7887만</t>
-  </si>
-  <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>POSCO</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=POSCO</t>
-  </si>
-  <si>
-    <t>143조 3408억 6701만</t>
-  </si>
-  <si>
     <t>루넨</t>
   </si>
   <si>
@@ -633,9 +636,6 @@
     <t>55조 7049억 3694만</t>
   </si>
   <si>
-    <t>28</t>
-  </si>
-  <si>
     <t>악의꽃</t>
   </si>
   <si>
@@ -675,7 +675,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8B%B8%EB%A4%BD</t>
   </si>
   <si>
-    <t>8경 4605조 5179억 3801만</t>
+    <t>8경 6327조 6013억 9186만</t>
   </si>
   <si>
     <t>신궁쨩</t>
@@ -783,6 +783,15 @@
     <t>180조 1511억 6313만</t>
   </si>
   <si>
+    <t>경특</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B2%BD%ED%8A%B9</t>
+  </si>
+  <si>
+    <t>125조 4342억 3651만</t>
+  </si>
+  <si>
     <t>땩콩</t>
   </si>
   <si>
@@ -813,15 +822,6 @@
     <t>122조 668억 9161만</t>
   </si>
   <si>
-    <t>경특</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B2%BD%ED%8A%B9</t>
-  </si>
-  <si>
-    <t>119조 7499억 1993만</t>
-  </si>
-  <si>
     <t>봄녘</t>
   </si>
   <si>
@@ -891,7 +891,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8B%A4%EC%86%A1%EC%9D%B4</t>
   </si>
   <si>
-    <t>30조 8752억 547만</t>
+    <t>33조 3902억 7692만</t>
   </si>
   <si>
     <t>빠나쨩</t>
@@ -963,7 +963,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%9C%EB%84%AC</t>
   </si>
   <si>
-    <t>2375조 8543억 1894만</t>
+    <t>2507조 4446억 8062만</t>
   </si>
   <si>
     <t>임순이</t>
@@ -990,7 +990,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B0%80%ED%94%84%ED%91%B8%EC%94%A8</t>
   </si>
   <si>
-    <t>1775조 5915억 3045만</t>
+    <t>1791조 9945억 7647만</t>
   </si>
   <si>
     <t>쑥국</t>
@@ -1053,7 +1053,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%85%B8%EB%93%9D</t>
   </si>
   <si>
-    <t>348조 9207억 6037만</t>
+    <t>349조 435억 3882만</t>
   </si>
   <si>
     <t>핫장</t>
@@ -1062,7 +1062,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%AB%EC%9E%A5</t>
   </si>
   <si>
-    <t>254조 3992억 7562만</t>
+    <t>254조 6182억 4665만</t>
   </si>
   <si>
     <t>겸찰</t>
@@ -1098,7 +1098,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B0%9C%EC%A0%90</t>
   </si>
   <si>
-    <t>190조 2848억 2308만</t>
+    <t>191조 6596억 3475만</t>
   </si>
   <si>
     <t>키은</t>
@@ -1179,7 +1179,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B1%A0%EC%9E%AC%EB%B2%94</t>
   </si>
   <si>
-    <t>66조 3840억 5859만</t>
+    <t>68조 277억 3204만</t>
   </si>
   <si>
     <t>핫두</t>
@@ -1188,7 +1188,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%AB%EB%91%90</t>
   </si>
   <si>
-    <t>59조 2713억 6623만</t>
+    <t>59조 8128억 2165만</t>
   </si>
   <si>
     <t>까사PC</t>
@@ -1788,7 +1788,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B0%AF%EC%88%98%EC%9A%A9</t>
   </si>
   <si>
-    <t>1190조 6095억 7843만</t>
+    <t>1220조 1789억 2840만</t>
   </si>
   <si>
     <t>심천</t>
@@ -1968,7 +1968,7 @@
     <t>https://mgf.gg/contents/character.php?n=57%EB%85%84%EA%B9%80%EC%B6%98%EB%B0%B0</t>
   </si>
   <si>
-    <t>15조 5318억 9821만</t>
+    <t>15조 5820억 6189만</t>
   </si>
   <si>
     <t>킴밍끼</t>
@@ -1998,7 +1998,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A9%94%EB%A6%B0%EC%9D%B4%EC%9D%B4</t>
   </si>
   <si>
-    <t>10조 2452억 7329만</t>
+    <t>10조 3519억 8814만</t>
   </si>
   <si>
     <t>먕겜</t>
@@ -2638,7 +2638,7 @@
     <col min="5" max="5" width="16.7109375" customWidth="1"/>
     <col min="6" max="8" width="13.7109375" customWidth="1"/>
     <col min="9" max="9" width="14.7109375" customWidth="1"/>
-    <col min="10" max="10" width="23.7109375" customWidth="1"/>
+    <col min="10" max="10" width="22.7109375" customWidth="1"/>
     <col min="11" max="11" width="50.7109375" customWidth="1"/>
     <col min="12" max="12" width="19.7109375" customWidth="1"/>
     <col min="13" max="13" width="12.7109375" customWidth="1"/>
@@ -3519,16 +3519,16 @@
         <v>13</v>
       </c>
       <c r="B17" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C17" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="D17" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="E17" s="2" t="s">
         <v>155</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>156</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>83</v>
@@ -3540,7 +3540,7 @@
         <v>126</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -3551,7 +3551,7 @@
         <v>13</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>28</v>
+        <v>157</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>158</v>
@@ -3743,16 +3743,16 @@
         <v>13</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>51</v>
+        <v>182</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>83</v>
@@ -3764,7 +3764,7 @@
         <v>126</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -3775,16 +3775,16 @@
         <v>13</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>83</v>
@@ -3796,7 +3796,7 @@
         <v>144</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -3807,28 +3807,28 @@
         <v>13</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>67</v>
+        <v>44</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>83</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="H26" s="2" t="s">
         <v>144</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -3848,19 +3848,19 @@
         <v>23</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>90</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -3871,16 +3871,16 @@
         <v>13</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>17</v>
+        <v>67</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>83</v>
@@ -3889,10 +3889,10 @@
         <v>111</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -3903,7 +3903,7 @@
         <v>13</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>200</v>
+        <v>17</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>201</v>
@@ -3953,7 +3953,7 @@
         <v>160</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>208</v>
@@ -3985,7 +3985,7 @@
         <v>90</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I31" s="2" t="s">
         <v>211</v>
@@ -4483,10 +4483,10 @@
         <v>83</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>160</v>
+        <v>106</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>252</v>
@@ -4515,13 +4515,13 @@
         <v>83</v>
       </c>
       <c r="G15" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="I15" s="2" t="s">
         <v>255</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>256</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -4535,22 +4535,22 @@
         <v>150</v>
       </c>
       <c r="C16" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="E16" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="D16" s="2" t="s">
-        <v>257</v>
-      </c>
-      <c r="E16" s="2" t="s">
+      <c r="F16" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="G16" s="2" t="s">
         <v>258</v>
       </c>
-      <c r="F16" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>190</v>
-      </c>
       <c r="H16" s="2" t="s">
-        <v>194</v>
+        <v>144</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>259</v>
@@ -4564,7 +4564,7 @@
         <v>25</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>154</v>
+        <v>28</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>260</v>
@@ -4579,10 +4579,10 @@
         <v>83</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>106</v>
+        <v>191</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>262</v>
@@ -4596,7 +4596,7 @@
         <v>25</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>28</v>
+        <v>157</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>263</v>
@@ -4614,7 +4614,7 @@
         <v>84</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>265</v>
@@ -4646,7 +4646,7 @@
         <v>160</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>268</v>
@@ -4710,7 +4710,7 @@
         <v>106</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>274</v>
@@ -4774,7 +4774,7 @@
         <v>90</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>280</v>
@@ -4788,7 +4788,7 @@
         <v>25</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>51</v>
+        <v>182</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>281</v>
@@ -4820,7 +4820,7 @@
         <v>25</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>284</v>
@@ -4852,7 +4852,7 @@
         <v>25</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>67</v>
+        <v>44</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>287</v>
@@ -4899,7 +4899,7 @@
         <v>83</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="H27" s="2" t="s">
         <v>292</v>
@@ -4916,7 +4916,7 @@
         <v>25</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>17</v>
+        <v>67</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>294</v>
@@ -4948,7 +4948,7 @@
         <v>25</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>200</v>
+        <v>17</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>298</v>
@@ -4992,7 +4992,7 @@
         <v>301</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>90</v>
@@ -5108,7 +5108,7 @@
         <v>303</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>106</v>
@@ -5576,7 +5576,7 @@
         <v>34</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>154</v>
+        <v>28</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>347</v>
@@ -5608,7 +5608,7 @@
         <v>34</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>28</v>
+        <v>157</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>350</v>
@@ -5754,7 +5754,7 @@
         <v>160</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>364</v>
@@ -5800,7 +5800,7 @@
         <v>34</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>51</v>
+        <v>182</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>368</v>
@@ -5818,7 +5818,7 @@
         <v>160</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>370</v>
@@ -5832,7 +5832,7 @@
         <v>34</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>371</v>
@@ -5864,7 +5864,7 @@
         <v>34</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>67</v>
+        <v>44</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>374</v>
@@ -5882,7 +5882,7 @@
         <v>90</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>376</v>
@@ -5914,7 +5914,7 @@
         <v>84</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>379</v>
@@ -5928,7 +5928,7 @@
         <v>34</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>17</v>
+        <v>67</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>380</v>
@@ -5946,7 +5946,7 @@
         <v>100</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>382</v>
@@ -5960,7 +5960,7 @@
         <v>34</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>200</v>
+        <v>17</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>383</v>
@@ -6185,7 +6185,7 @@
         <v>395</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>90</v>
@@ -6621,7 +6621,7 @@
         <v>41</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>154</v>
+        <v>28</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>438</v>
@@ -6653,7 +6653,7 @@
         <v>41</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>28</v>
+        <v>157</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>441</v>
@@ -6668,10 +6668,10 @@
         <v>83</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>443</v>
@@ -6703,7 +6703,7 @@
         <v>160</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>446</v>
@@ -6767,7 +6767,7 @@
         <v>84</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>452</v>
@@ -6799,7 +6799,7 @@
         <v>90</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>455</v>
@@ -6831,7 +6831,7 @@
         <v>106</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>458</v>
@@ -6845,7 +6845,7 @@
         <v>41</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>51</v>
+        <v>182</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>459</v>
@@ -6863,7 +6863,7 @@
         <v>111</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>461</v>
@@ -6877,7 +6877,7 @@
         <v>41</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>462</v>
@@ -6895,7 +6895,7 @@
         <v>90</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>464</v>
@@ -6909,7 +6909,7 @@
         <v>41</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>67</v>
+        <v>44</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>465</v>
@@ -6927,7 +6927,7 @@
         <v>90</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>467</v>
@@ -6973,7 +6973,7 @@
         <v>41</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>17</v>
+        <v>67</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>471</v>
@@ -6991,7 +6991,7 @@
         <v>135</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>473</v>
@@ -7005,7 +7005,7 @@
         <v>41</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>200</v>
+        <v>17</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>474</v>
@@ -7265,7 +7265,7 @@
         <v>83</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>91</v>
@@ -7454,7 +7454,7 @@
         <v>507</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>84</v>
@@ -7649,7 +7649,7 @@
         <v>83</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>144</v>
@@ -7666,7 +7666,7 @@
         <v>48</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>154</v>
+        <v>28</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>527</v>
@@ -7698,7 +7698,7 @@
         <v>48</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>28</v>
+        <v>157</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>530</v>
@@ -7812,7 +7812,7 @@
         <v>111</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>541</v>
@@ -7844,7 +7844,7 @@
         <v>84</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>544</v>
@@ -7873,10 +7873,10 @@
         <v>83</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>547</v>
@@ -7890,7 +7890,7 @@
         <v>48</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>51</v>
+        <v>182</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>548</v>
@@ -7908,7 +7908,7 @@
         <v>160</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>550</v>
@@ -7922,7 +7922,7 @@
         <v>48</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>551</v>
@@ -7940,7 +7940,7 @@
         <v>100</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>553</v>
@@ -7954,7 +7954,7 @@
         <v>48</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>67</v>
+        <v>44</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>554</v>
@@ -8018,7 +8018,7 @@
         <v>48</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>17</v>
+        <v>67</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>560</v>
@@ -8050,7 +8050,7 @@
         <v>48</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>200</v>
+        <v>17</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>563</v>
@@ -8370,7 +8370,7 @@
         <v>584</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>106</v>
@@ -8536,7 +8536,7 @@
         <v>111</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>600</v>
@@ -8664,7 +8664,7 @@
         <v>90</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>612</v>
@@ -8678,7 +8678,7 @@
         <v>56</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>154</v>
+        <v>28</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>613</v>
@@ -8693,10 +8693,10 @@
         <v>83</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>615</v>
@@ -8710,7 +8710,7 @@
         <v>56</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>28</v>
+        <v>157</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>616</v>
@@ -8725,10 +8725,10 @@
         <v>83</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>618</v>
@@ -8760,7 +8760,7 @@
         <v>90</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>621</v>
@@ -8792,7 +8792,7 @@
         <v>160</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>624</v>
@@ -8856,7 +8856,7 @@
         <v>160</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>630</v>
@@ -8885,7 +8885,7 @@
         <v>83</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="H23" s="2" t="s">
         <v>292</v>
@@ -8902,7 +8902,7 @@
         <v>56</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>51</v>
+        <v>182</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>634</v>
@@ -8934,7 +8934,7 @@
         <v>56</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>637</v>
@@ -8966,7 +8966,7 @@
         <v>56</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>67</v>
+        <v>44</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>640</v>
@@ -9030,7 +9030,7 @@
         <v>56</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>17</v>
+        <v>67</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>646</v>
@@ -9062,7 +9062,7 @@
         <v>56</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>200</v>
+        <v>17</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>650</v>
@@ -9452,7 +9452,7 @@
         <v>106</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>679</v>
@@ -9484,7 +9484,7 @@
         <v>160</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>682</v>
@@ -9516,7 +9516,7 @@
         <v>90</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>685</v>
@@ -9542,13 +9542,13 @@
         <v>686</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>100</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>687</v>
@@ -9580,7 +9580,7 @@
         <v>106</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>690</v>
@@ -9612,7 +9612,7 @@
         <v>90</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>693</v>
@@ -9690,7 +9690,7 @@
         <v>64</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>154</v>
+        <v>28</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>700</v>
@@ -9722,7 +9722,7 @@
         <v>64</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>28</v>
+        <v>157</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>703</v>
@@ -9740,7 +9740,7 @@
         <v>100</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>705</v>
@@ -9914,7 +9914,7 @@
         <v>64</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>51</v>
+        <v>182</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>721</v>
@@ -9929,7 +9929,7 @@
         <v>83</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="H24" s="2" t="s">
         <v>292</v>
@@ -9946,7 +9946,7 @@
         <v>64</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>724</v>
@@ -9978,7 +9978,7 @@
         <v>64</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>67</v>
+        <v>44</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>727</v>
@@ -10042,7 +10042,7 @@
         <v>64</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>17</v>
+        <v>67</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>733</v>
@@ -10074,7 +10074,7 @@
         <v>64</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>200</v>
+        <v>17</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>736</v>
